--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,10 +3808,10 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>865.73</v>
+        <v>861</v>
       </c>
       <c r="J7" t="n">
-        <v>163.77</v>
+        <v>163.61</v>
       </c>
     </row>
     <row r="8">
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1466000</v>
+        <v>1418000</v>
       </c>
       <c r="J8" t="n">
-        <v>580750.16</v>
+        <v>574122.8</v>
       </c>
     </row>
     <row r="9">
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>235000</v>
+        <v>231500</v>
       </c>
       <c r="J9" t="n">
         <v>75198.12</v>
@@ -3910,10 +3910,10 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>47730</v>
+        <v>48010</v>
       </c>
       <c r="J10" t="n">
-        <v>13503.49</v>
+        <v>13532.64</v>
       </c>
     </row>
     <row r="11">
@@ -3944,10 +3944,10 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1215.98</v>
+        <v>1237.92</v>
       </c>
       <c r="J11" t="n">
-        <v>237.45</v>
+        <v>237.3</v>
       </c>
     </row>
   </sheetData>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>861</v>
+        <v>868.52</v>
       </c>
       <c r="J7" t="n">
         <v>163.61</v>
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1418000</v>
+        <v>1433000</v>
       </c>
       <c r="J8" t="n">
         <v>574122.8</v>
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>231500</v>
+        <v>241000</v>
       </c>
       <c r="J9" t="n">
         <v>75198.12</v>
@@ -3944,10 +3944,10 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1237.92</v>
+        <v>1271.05</v>
       </c>
       <c r="J11" t="n">
-        <v>237.3</v>
+        <v>236.66</v>
       </c>
     </row>
   </sheetData>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>868.52</v>
+        <v>911.29</v>
       </c>
       <c r="J7" t="n">
         <v>163.61</v>
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1433000</v>
+        <v>1521000</v>
       </c>
       <c r="J8" t="n">
         <v>574122.8</v>
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>241000</v>
+        <v>258000</v>
       </c>
       <c r="J9" t="n">
         <v>75198.12</v>
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>48010</v>
+        <v>49870</v>
       </c>
       <c r="J10" t="n">
         <v>13532.64</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1271.05</v>
+        <v>1344.29</v>
       </c>
       <c r="J11" t="n">
         <v>236.66</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>911.29</v>
+        <v>949.83</v>
       </c>
       <c r="J7" t="n">
         <v>163.61</v>
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1521000</v>
+        <v>1572000</v>
       </c>
       <c r="J8" t="n">
-        <v>574122.8</v>
+        <v>573669.03</v>
       </c>
     </row>
     <row r="9">
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>258000</v>
+        <v>263000</v>
       </c>
       <c r="J9" t="n">
         <v>75198.12</v>
@@ -3910,10 +3910,10 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>49870</v>
+        <v>51800</v>
       </c>
       <c r="J10" t="n">
-        <v>13532.64</v>
+        <v>13680.85</v>
       </c>
     </row>
     <row r="11">
@@ -3944,10 +3944,10 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1344.29</v>
+        <v>1528.11</v>
       </c>
       <c r="J11" t="n">
-        <v>236.66</v>
+        <v>237.49</v>
       </c>
     </row>
   </sheetData>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>949.83</v>
+        <v>971.66</v>
       </c>
       <c r="J7" t="n">
         <v>163.61</v>
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1572000</v>
+        <v>1667000</v>
       </c>
       <c r="J8" t="n">
         <v>573669.03</v>
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>263000</v>
+        <v>274500</v>
       </c>
       <c r="J9" t="n">
         <v>75198.12</v>
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>51800</v>
+        <v>53740</v>
       </c>
       <c r="J10" t="n">
         <v>13680.85</v>
@@ -3944,10 +3944,10 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1528.11</v>
+        <v>1641.11</v>
       </c>
       <c r="J11" t="n">
-        <v>237.49</v>
+        <v>238.25</v>
       </c>
     </row>
   </sheetData>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>971.66</v>
+        <v>1011.75</v>
       </c>
       <c r="J7" t="n">
         <v>163.61</v>
@@ -3845,7 +3845,7 @@
         <v>1667000</v>
       </c>
       <c r="J8" t="n">
-        <v>573669.03</v>
+        <v>566381.03</v>
       </c>
     </row>
     <row r="9">
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>53740</v>
+        <v>61840</v>
       </c>
       <c r="J10" t="n">
         <v>13680.85</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1641.11</v>
+        <v>1786.85</v>
       </c>
       <c r="J11" t="n">
         <v>238.25</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>1011.75</v>
+        <v>940.76</v>
       </c>
       <c r="J7" t="n">
         <v>163.61</v>
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1667000</v>
+        <v>1621000</v>
       </c>
       <c r="J8" t="n">
         <v>566381.03</v>
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>274500</v>
+        <v>263500</v>
       </c>
       <c r="J9" t="n">
         <v>75198.12</v>
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>61840</v>
+        <v>57150</v>
       </c>
       <c r="J10" t="n">
         <v>13680.85</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1786.85</v>
+        <v>1625.78</v>
       </c>
       <c r="J11" t="n">
         <v>238.25</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>940.76</v>
+        <v>937.11</v>
       </c>
       <c r="J7" t="n">
         <v>163.61</v>
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1621000</v>
+        <v>1624000</v>
       </c>
       <c r="J8" t="n">
-        <v>566381.03</v>
+        <v>565756.14</v>
       </c>
     </row>
     <row r="9">
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>263500</v>
+        <v>257500</v>
       </c>
       <c r="J9" t="n">
         <v>75198.12</v>
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>57150</v>
+        <v>49950</v>
       </c>
       <c r="J10" t="n">
         <v>13680.85</v>
@@ -3944,10 +3944,10 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1625.78</v>
+        <v>1568.87</v>
       </c>
       <c r="J11" t="n">
-        <v>238.25</v>
+        <v>237.71</v>
       </c>
     </row>
   </sheetData>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,10 +3808,10 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>937.11</v>
+        <v>974.33</v>
       </c>
       <c r="J7" t="n">
-        <v>163.61</v>
+        <v>163.85</v>
       </c>
     </row>
     <row r="8">
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1624000</v>
+        <v>1710000</v>
       </c>
       <c r="J8" t="n">
-        <v>565756.14</v>
+        <v>566102.46</v>
       </c>
     </row>
     <row r="9">
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>257500</v>
+        <v>273000</v>
       </c>
       <c r="J9" t="n">
         <v>75198.12</v>
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>49950</v>
+        <v>52950</v>
       </c>
       <c r="J10" t="n">
         <v>13680.85</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1568.87</v>
+        <v>1600.62</v>
       </c>
       <c r="J11" t="n">
         <v>237.71</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>974.33</v>
+        <v>966.78</v>
       </c>
       <c r="J7" t="n">
         <v>163.85</v>
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1710000</v>
+        <v>1761000</v>
       </c>
       <c r="J8" t="n">
         <v>566102.46</v>
@@ -3876,10 +3876,10 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>273000</v>
+        <v>270000</v>
       </c>
       <c r="J9" t="n">
-        <v>75198.12</v>
+        <v>75198.3</v>
       </c>
     </row>
     <row r="10">
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>52950</v>
+        <v>54320</v>
       </c>
       <c r="J10" t="n">
         <v>13680.85</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1600.62</v>
+        <v>1596.08</v>
       </c>
       <c r="J11" t="n">
         <v>237.71</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>966.78</v>
+        <v>897.3150000000001</v>
       </c>
       <c r="J7" t="n">
         <v>163.85</v>
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1761000</v>
+        <v>1664000</v>
       </c>
       <c r="J8" t="n">
         <v>566102.46</v>
@@ -3876,10 +3876,10 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>270000</v>
+        <v>256000</v>
       </c>
       <c r="J9" t="n">
-        <v>75198.3</v>
+        <v>75326.22</v>
       </c>
     </row>
     <row r="10">
@@ -3910,10 +3910,10 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>54320</v>
+        <v>50930</v>
       </c>
       <c r="J10" t="n">
-        <v>13680.85</v>
+        <v>13692.57</v>
       </c>
     </row>
     <row r="11">
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1596.08</v>
+        <v>1460.99</v>
       </c>
       <c r="J11" t="n">
         <v>237.71</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>897.3150000000001</v>
+        <v>932.97</v>
       </c>
       <c r="J7" t="n">
         <v>163.85</v>
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1664000</v>
+        <v>1715000</v>
       </c>
       <c r="J8" t="n">
-        <v>566102.46</v>
+        <v>567719.48</v>
       </c>
     </row>
     <row r="9">
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>256000</v>
+        <v>261000</v>
       </c>
       <c r="J9" t="n">
         <v>75326.22</v>
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>50930</v>
+        <v>51260</v>
       </c>
       <c r="J10" t="n">
         <v>13692.57</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1460.99</v>
+        <v>1480.77</v>
       </c>
       <c r="J11" t="n">
         <v>237.71</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,10 +3808,10 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>932.97</v>
+        <v>938.4</v>
       </c>
       <c r="J7" t="n">
-        <v>163.85</v>
+        <v>163.76</v>
       </c>
     </row>
     <row r="8">
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1715000</v>
+        <v>1680000</v>
       </c>
       <c r="J8" t="n">
-        <v>567719.48</v>
+        <v>567859.9300000001</v>
       </c>
     </row>
     <row r="9">
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>261000</v>
+        <v>259500</v>
       </c>
       <c r="J9" t="n">
         <v>75326.22</v>
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>51260</v>
+        <v>50000</v>
       </c>
       <c r="J10" t="n">
         <v>13692.57</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1480.77</v>
+        <v>1499.37</v>
       </c>
       <c r="J11" t="n">
         <v>237.71</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>938.4</v>
+        <v>935.39</v>
       </c>
       <c r="J7" t="n">
         <v>163.76</v>
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1680000</v>
+        <v>1743000</v>
       </c>
       <c r="J8" t="n">
         <v>567859.9300000001</v>
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>259500</v>
+        <v>267000</v>
       </c>
       <c r="J9" t="n">
         <v>75326.22</v>
@@ -3910,10 +3910,10 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>50000</v>
+        <v>52500</v>
       </c>
       <c r="J10" t="n">
-        <v>13692.57</v>
+        <v>13767.54</v>
       </c>
     </row>
     <row r="11">
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1499.37</v>
+        <v>1484.95</v>
       </c>
       <c r="J11" t="n">
         <v>237.71</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>935.39</v>
+        <v>932.86</v>
       </c>
       <c r="J7" t="n">
         <v>163.76</v>
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1743000</v>
+        <v>1658000</v>
       </c>
       <c r="J8" t="n">
         <v>567859.9300000001</v>
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>267000</v>
+        <v>256500</v>
       </c>
       <c r="J9" t="n">
         <v>75326.22</v>
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>52500</v>
+        <v>47900</v>
       </c>
       <c r="J10" t="n">
         <v>13767.54</v>
@@ -3944,10 +3944,10 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1484.95</v>
+        <v>1484.98</v>
       </c>
       <c r="J11" t="n">
-        <v>237.71</v>
+        <v>237.54</v>
       </c>
     </row>
   </sheetData>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,10 +3808,10 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>932.86</v>
+        <v>933.4400000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>163.76</v>
+        <v>165.19</v>
       </c>
     </row>
     <row r="8">
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1658000</v>
+        <v>1652000</v>
       </c>
       <c r="J8" t="n">
-        <v>567859.9300000001</v>
+        <v>567980.54</v>
       </c>
     </row>
     <row r="9">
@@ -3876,10 +3876,10 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>256500</v>
+        <v>255000</v>
       </c>
       <c r="J9" t="n">
-        <v>75326.22</v>
+        <v>74958.73</v>
       </c>
     </row>
     <row r="10">
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>47900</v>
+        <v>51000</v>
       </c>
       <c r="J10" t="n">
         <v>13767.54</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1484.98</v>
+        <v>1536.87</v>
       </c>
       <c r="J11" t="n">
         <v>237.54</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>933.4400000000001</v>
+        <v>956.08</v>
       </c>
       <c r="J7" t="n">
         <v>165.19</v>
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1652000</v>
+        <v>1597000</v>
       </c>
       <c r="J8" t="n">
-        <v>567980.54</v>
+        <v>566036.03</v>
       </c>
     </row>
     <row r="9">
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>255000</v>
+        <v>248500</v>
       </c>
       <c r="J9" t="n">
         <v>74958.73</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1536.87</v>
+        <v>1553.4</v>
       </c>
       <c r="J11" t="n">
         <v>237.54</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>956.08</v>
+        <v>958.16</v>
       </c>
       <c r="J7" t="n">
         <v>165.19</v>
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1597000</v>
+        <v>1580000</v>
       </c>
       <c r="J8" t="n">
         <v>566036.03</v>
@@ -3876,10 +3876,10 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>248500</v>
+        <v>248000</v>
       </c>
       <c r="J9" t="n">
-        <v>74958.73</v>
+        <v>74765.91</v>
       </c>
     </row>
     <row r="10">
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>51000</v>
+        <v>51670</v>
       </c>
       <c r="J10" t="n">
         <v>13767.54</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1553.4</v>
+        <v>1554.99</v>
       </c>
       <c r="J11" t="n">
         <v>237.54</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>958.16</v>
+        <v>1016.59</v>
       </c>
       <c r="J7" t="n">
         <v>165.19</v>
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1580000</v>
+        <v>1662000</v>
       </c>
       <c r="J8" t="n">
         <v>566036.03</v>
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>248000</v>
+        <v>257000</v>
       </c>
       <c r="J9" t="n">
         <v>74765.91</v>
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>51670</v>
+        <v>54460</v>
       </c>
       <c r="J10" t="n">
         <v>13767.54</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1554.99</v>
+        <v>1740</v>
       </c>
       <c r="J11" t="n">
         <v>237.54</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>1016.59</v>
+        <v>1000.26</v>
       </c>
       <c r="J7" t="n">
         <v>165.19</v>
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1662000</v>
+        <v>1814000</v>
       </c>
       <c r="J8" t="n">
         <v>566036.03</v>
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>257000</v>
+        <v>272000</v>
       </c>
       <c r="J9" t="n">
         <v>74765.91</v>
@@ -3910,10 +3910,10 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>54460</v>
+        <v>57410</v>
       </c>
       <c r="J10" t="n">
-        <v>13767.54</v>
+        <v>14530.9</v>
       </c>
     </row>
     <row r="11">
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1740</v>
+        <v>1737.99</v>
       </c>
       <c r="J11" t="n">
         <v>237.54</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>1000.26</v>
+        <v>1027.77</v>
       </c>
       <c r="J7" t="n">
         <v>165.19</v>
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1814000</v>
+        <v>1832000</v>
       </c>
       <c r="J8" t="n">
-        <v>566036.03</v>
+        <v>566534.38</v>
       </c>
     </row>
     <row r="9">
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>272000</v>
+        <v>267500</v>
       </c>
       <c r="J9" t="n">
         <v>74765.91</v>
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>57410</v>
+        <v>57000</v>
       </c>
       <c r="J10" t="n">
         <v>14530.9</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1737.99</v>
+        <v>1764.17</v>
       </c>
       <c r="J11" t="n">
         <v>237.54</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>1027.77</v>
+        <v>977.41</v>
       </c>
       <c r="J7" t="n">
         <v>165.19</v>
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1832000</v>
+        <v>1850000</v>
       </c>
       <c r="J8" t="n">
-        <v>566534.38</v>
+        <v>571194.72</v>
       </c>
     </row>
     <row r="9">
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>267500</v>
+        <v>266500</v>
       </c>
       <c r="J9" t="n">
         <v>74765.91</v>
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>57000</v>
+        <v>58090</v>
       </c>
       <c r="J10" t="n">
         <v>14530.9</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1764.17</v>
+        <v>1692.59</v>
       </c>
       <c r="J11" t="n">
         <v>237.54</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,10 +3808,10 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>977.41</v>
+        <v>975.26</v>
       </c>
       <c r="J7" t="n">
-        <v>165.19</v>
+        <v>165.31</v>
       </c>
     </row>
     <row r="8">
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1850000</v>
+        <v>1832000</v>
       </c>
       <c r="J8" t="n">
-        <v>571194.72</v>
+        <v>570340.59</v>
       </c>
     </row>
     <row r="9">
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>266500</v>
+        <v>262000</v>
       </c>
       <c r="J9" t="n">
         <v>74765.91</v>
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>58090</v>
+        <v>54030</v>
       </c>
       <c r="J10" t="n">
         <v>14530.9</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1692.59</v>
+        <v>1633.35</v>
       </c>
       <c r="J11" t="n">
         <v>237.54</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,10 +3808,10 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>975.26</v>
+        <v>914.9349999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>165.31</v>
+        <v>165.36</v>
       </c>
     </row>
     <row r="8">
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1832000</v>
+        <v>1697000</v>
       </c>
       <c r="J8" t="n">
-        <v>570340.59</v>
+        <v>569608.24</v>
       </c>
     </row>
     <row r="9">
@@ -3876,10 +3876,10 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>262000</v>
+        <v>249000</v>
       </c>
       <c r="J9" t="n">
-        <v>74765.91</v>
+        <v>74214.64</v>
       </c>
     </row>
     <row r="10">
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>54030</v>
+        <v>50590</v>
       </c>
       <c r="J10" t="n">
         <v>14530.9</v>
@@ -3944,10 +3944,10 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1633.35</v>
+        <v>1533.09</v>
       </c>
       <c r="J11" t="n">
-        <v>237.54</v>
+        <v>238.48</v>
       </c>
     </row>
   </sheetData>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,10 +3808,10 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>914.9349999999999</v>
+        <v>927.6</v>
       </c>
       <c r="J7" t="n">
-        <v>165.36</v>
+        <v>165.85</v>
       </c>
     </row>
     <row r="8">
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1697000</v>
+        <v>1690000</v>
       </c>
       <c r="J8" t="n">
-        <v>569608.24</v>
+        <v>569861.8199999999</v>
       </c>
     </row>
     <row r="9">
@@ -3876,10 +3876,10 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>249000</v>
+        <v>248500</v>
       </c>
       <c r="J9" t="n">
-        <v>74214.64</v>
+        <v>74238.89</v>
       </c>
     </row>
     <row r="10">
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>50590</v>
+        <v>51750</v>
       </c>
       <c r="J10" t="n">
         <v>14530.9</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1533.09</v>
+        <v>1530.895</v>
       </c>
       <c r="J11" t="n">
         <v>238.48</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,10 +3808,10 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>927.6</v>
+        <v>926.55</v>
       </c>
       <c r="J7" t="n">
-        <v>165.85</v>
+        <v>166.28</v>
       </c>
     </row>
     <row r="8">
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1690000</v>
+        <v>1759000</v>
       </c>
       <c r="J8" t="n">
         <v>569861.8199999999</v>
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>248500</v>
+        <v>253500</v>
       </c>
       <c r="J9" t="n">
         <v>74238.89</v>
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>51750</v>
+        <v>50780</v>
       </c>
       <c r="J10" t="n">
         <v>14530.9</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1530.895</v>
+        <v>1519.97</v>
       </c>
       <c r="J11" t="n">
         <v>238.48</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,10 +3808,10 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>926.55</v>
+        <v>977.5</v>
       </c>
       <c r="J7" t="n">
-        <v>166.28</v>
+        <v>166.37</v>
       </c>
     </row>
     <row r="8">
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1759000</v>
+        <v>1745000</v>
       </c>
       <c r="J8" t="n">
         <v>569861.8199999999</v>
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>253500</v>
+        <v>252500</v>
       </c>
       <c r="J9" t="n">
         <v>74238.89</v>
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>50780</v>
+        <v>49880</v>
       </c>
       <c r="J10" t="n">
         <v>14530.9</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1519.97</v>
+        <v>1614.39</v>
       </c>
       <c r="J11" t="n">
         <v>238.48</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>977.5</v>
+        <v>1015.8</v>
       </c>
       <c r="J7" t="n">
         <v>166.37</v>
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1745000</v>
+        <v>1857000</v>
       </c>
       <c r="J8" t="n">
         <v>569861.8199999999</v>
@@ -3876,10 +3876,10 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>252500</v>
+        <v>261000</v>
       </c>
       <c r="J9" t="n">
-        <v>74238.89</v>
+        <v>74019.07000000001</v>
       </c>
     </row>
     <row r="10">
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>49880</v>
+        <v>54570</v>
       </c>
       <c r="J10" t="n">
         <v>14530.9</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1614.39</v>
+        <v>1791.82</v>
       </c>
       <c r="J11" t="n">
         <v>238.48</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,10 +3808,10 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>1015.8</v>
+        <v>1043.96</v>
       </c>
       <c r="J7" t="n">
-        <v>166.37</v>
+        <v>168.49</v>
       </c>
     </row>
     <row r="8">
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1857000</v>
+        <v>1868000</v>
       </c>
       <c r="J8" t="n">
-        <v>569861.8199999999</v>
+        <v>490429.89</v>
       </c>
     </row>
     <row r="9">
@@ -3876,10 +3876,10 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>261000</v>
+        <v>274000</v>
       </c>
       <c r="J9" t="n">
-        <v>74019.07000000001</v>
+        <v>74006.14999999999</v>
       </c>
     </row>
     <row r="10">
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1791.82</v>
+        <v>1766.64</v>
       </c>
       <c r="J11" t="n">
         <v>238.48</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>1043.96</v>
+        <v>1096.16</v>
       </c>
       <c r="J7" t="n">
         <v>168.49</v>
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1868000</v>
+        <v>1840000</v>
       </c>
       <c r="J8" t="n">
         <v>490429.89</v>
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>274000</v>
+        <v>276500</v>
       </c>
       <c r="J9" t="n">
         <v>74006.14999999999</v>
@@ -3944,10 +3944,10 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1766.64</v>
+        <v>1887.04</v>
       </c>
       <c r="J11" t="n">
-        <v>238.48</v>
+        <v>238.08</v>
       </c>
     </row>
   </sheetData>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,10 +3808,10 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>1096.16</v>
+        <v>1071.88</v>
       </c>
       <c r="J7" t="n">
-        <v>168.49</v>
+        <v>168.85</v>
       </c>
     </row>
     <row r="8">
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1840000</v>
+        <v>1862000</v>
       </c>
       <c r="J8" t="n">
-        <v>490429.89</v>
+        <v>490807.53</v>
       </c>
     </row>
     <row r="9">
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>276500</v>
+        <v>285500</v>
       </c>
       <c r="J9" t="n">
         <v>74006.14999999999</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1887.04</v>
+        <v>1816.57</v>
       </c>
       <c r="J11" t="n">
         <v>238.08</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,10 +3808,10 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>1071.88</v>
+        <v>1056.384</v>
       </c>
       <c r="J7" t="n">
-        <v>168.85</v>
+        <v>168.98</v>
       </c>
     </row>
     <row r="8">
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>54570</v>
+        <v>54580</v>
       </c>
       <c r="J10" t="n">
         <v>14530.9</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1816.57</v>
+        <v>1760.647</v>
       </c>
       <c r="J11" t="n">
         <v>238.08</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,10 +3808,10 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>1056.384</v>
+        <v>1082.28</v>
       </c>
       <c r="J7" t="n">
-        <v>168.98</v>
+        <v>169.61</v>
       </c>
     </row>
     <row r="8">
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>54580</v>
+        <v>55780</v>
       </c>
       <c r="J10" t="n">
         <v>14530.9</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1760.647</v>
+        <v>1777.8</v>
       </c>
       <c r="J11" t="n">
         <v>238.08</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,10 +3808,10 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>1082.28</v>
+        <v>1053.98</v>
       </c>
       <c r="J7" t="n">
-        <v>169.61</v>
+        <v>171.51</v>
       </c>
     </row>
     <row r="8">
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1862000</v>
+        <v>1768000</v>
       </c>
       <c r="J8" t="n">
         <v>490807.53</v>
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>285500</v>
+        <v>270000</v>
       </c>
       <c r="J9" t="n">
         <v>74006.14999999999</v>
@@ -3910,10 +3910,10 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>55780</v>
+        <v>53340</v>
       </c>
       <c r="J10" t="n">
-        <v>14530.9</v>
+        <v>4843.64</v>
       </c>
     </row>
     <row r="11">
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1777.8</v>
+        <v>1712.89</v>
       </c>
       <c r="J11" t="n">
         <v>238.08</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,10 +3808,10 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>1053.98</v>
+        <v>1065.08</v>
       </c>
       <c r="J7" t="n">
-        <v>171.51</v>
+        <v>171.87</v>
       </c>
     </row>
     <row r="8">
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1768000</v>
+        <v>1765000</v>
       </c>
       <c r="J8" t="n">
-        <v>490807.53</v>
+        <v>489992.89</v>
       </c>
     </row>
     <row r="9">
@@ -3876,10 +3876,10 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>270000</v>
+        <v>272500</v>
       </c>
       <c r="J9" t="n">
-        <v>74006.14999999999</v>
+        <v>73814.3</v>
       </c>
     </row>
     <row r="10">
@@ -3910,10 +3910,10 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>53340</v>
+        <v>17880</v>
       </c>
       <c r="J10" t="n">
-        <v>4843.64</v>
+        <v>4860.41</v>
       </c>
     </row>
     <row r="11">
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1712.89</v>
+        <v>1729.76</v>
       </c>
       <c r="J11" t="n">
         <v>238.08</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>1065.08</v>
+        <v>1065.11</v>
       </c>
       <c r="J7" t="n">
         <v>171.87</v>
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1765000</v>
+        <v>1776000</v>
       </c>
       <c r="J8" t="n">
         <v>489992.89</v>
@@ -3876,10 +3876,10 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>272500</v>
+        <v>268500</v>
       </c>
       <c r="J9" t="n">
-        <v>73814.3</v>
+        <v>73876.69</v>
       </c>
     </row>
     <row r="10">
@@ -3910,10 +3910,10 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>17880</v>
+        <v>18095</v>
       </c>
       <c r="J10" t="n">
-        <v>4860.41</v>
+        <v>4859.95</v>
       </c>
     </row>
     <row r="11">
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1729.76</v>
+        <v>1739.89</v>
       </c>
       <c r="J11" t="n">
         <v>238.08</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,10 +3808,10 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>1065.11</v>
+        <v>1097.39</v>
       </c>
       <c r="J7" t="n">
-        <v>171.87</v>
+        <v>185.93</v>
       </c>
     </row>
     <row r="8">
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1776000</v>
+        <v>1833000</v>
       </c>
       <c r="J8" t="n">
         <v>489992.89</v>
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>268500</v>
+        <v>276000</v>
       </c>
       <c r="J9" t="n">
         <v>73876.69</v>
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>18095</v>
+        <v>19100</v>
       </c>
       <c r="J10" t="n">
         <v>4859.95</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1739.89</v>
+        <v>1787.69</v>
       </c>
       <c r="J11" t="n">
         <v>238.08</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,10 +3808,10 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>1097.39</v>
+        <v>1074.89</v>
       </c>
       <c r="J7" t="n">
-        <v>185.93</v>
+        <v>186.51</v>
       </c>
     </row>
     <row r="8">
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1833000</v>
+        <v>1841000</v>
       </c>
       <c r="J8" t="n">
         <v>489992.89</v>
@@ -3910,10 +3910,10 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>19100</v>
+        <v>19300</v>
       </c>
       <c r="J10" t="n">
-        <v>4859.95</v>
+        <v>4859.08</v>
       </c>
     </row>
     <row r="11">
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1787.69</v>
+        <v>1719.99</v>
       </c>
       <c r="J11" t="n">
         <v>238.08</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,10 +3808,10 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>1074.89</v>
+        <v>1068.73</v>
       </c>
       <c r="J7" t="n">
-        <v>186.51</v>
+        <v>187.08</v>
       </c>
     </row>
     <row r="8">
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1841000</v>
+        <v>1773000</v>
       </c>
       <c r="J8" t="n">
         <v>489992.89</v>
@@ -3876,10 +3876,10 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>276000</v>
+        <v>272000</v>
       </c>
       <c r="J9" t="n">
-        <v>73876.69</v>
+        <v>73998.71000000001</v>
       </c>
     </row>
     <row r="10">
@@ -3910,10 +3910,10 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>19300</v>
+        <v>18735</v>
       </c>
       <c r="J10" t="n">
-        <v>4859.08</v>
+        <v>4818.67</v>
       </c>
     </row>
     <row r="11">
@@ -3944,10 +3944,10 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1719.99</v>
+        <v>1678.79</v>
       </c>
       <c r="J11" t="n">
-        <v>238.08</v>
+        <v>239.7</v>
       </c>
     </row>
   </sheetData>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>1068.73</v>
+        <v>1024.645</v>
       </c>
       <c r="J7" t="n">
         <v>187.08</v>
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1773000</v>
+        <v>1681000</v>
       </c>
       <c r="J8" t="n">
-        <v>489992.89</v>
+        <v>489535.2</v>
       </c>
     </row>
     <row r="9">
@@ -3876,10 +3876,10 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>272000</v>
+        <v>262000</v>
       </c>
       <c r="J9" t="n">
-        <v>73998.71000000001</v>
+        <v>74718.08</v>
       </c>
     </row>
     <row r="10">
@@ -3910,10 +3910,10 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>18735</v>
+        <v>17505</v>
       </c>
       <c r="J10" t="n">
-        <v>4818.67</v>
+        <v>5022.49</v>
       </c>
     </row>
     <row r="11">
@@ -3944,10 +3944,10 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1678.79</v>
+        <v>1599.877</v>
       </c>
       <c r="J11" t="n">
-        <v>239.7</v>
+        <v>239.97</v>
       </c>
     </row>
   </sheetData>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>1024.645</v>
+        <v>989.04</v>
       </c>
       <c r="J7" t="n">
         <v>187.08</v>
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1681000</v>
+        <v>1605000</v>
       </c>
       <c r="J8" t="n">
-        <v>489535.2</v>
+        <v>488486.58</v>
       </c>
     </row>
     <row r="9">
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>262000</v>
+        <v>250500</v>
       </c>
       <c r="J9" t="n">
         <v>74718.08</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1599.877</v>
+        <v>1487.33</v>
       </c>
       <c r="J11" t="n">
         <v>239.97</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>989.04</v>
+        <v>953.1900000000001</v>
       </c>
       <c r="J7" t="n">
         <v>187.08</v>
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1605000</v>
+        <v>1443000</v>
       </c>
       <c r="J8" t="n">
         <v>488486.58</v>
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>250500</v>
+        <v>232000</v>
       </c>
       <c r="J9" t="n">
         <v>74718.08</v>
@@ -3910,10 +3910,10 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>17505</v>
+        <v>15180</v>
       </c>
       <c r="J10" t="n">
-        <v>5022.49</v>
+        <v>4818.27</v>
       </c>
     </row>
     <row r="11">
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1487.33</v>
+        <v>1482.33</v>
       </c>
       <c r="J11" t="n">
         <v>239.97</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>953.1900000000001</v>
+        <v>914.13</v>
       </c>
       <c r="J7" t="n">
         <v>187.08</v>
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1443000</v>
+        <v>1419000</v>
       </c>
       <c r="J8" t="n">
         <v>488486.58</v>
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>15180</v>
+        <v>14690</v>
       </c>
       <c r="J10" t="n">
         <v>4818.27</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1482.33</v>
+        <v>1403.34</v>
       </c>
       <c r="J11" t="n">
         <v>239.97</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,10 +3808,10 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>914.13</v>
+        <v>931.24</v>
       </c>
       <c r="J7" t="n">
-        <v>187.08</v>
+        <v>187.56</v>
       </c>
     </row>
     <row r="8">
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1419000</v>
+        <v>1262000</v>
       </c>
       <c r="J8" t="n">
         <v>488486.58</v>
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>232000</v>
+        <v>210000</v>
       </c>
       <c r="J9" t="n">
         <v>74718.08</v>
@@ -3910,10 +3910,10 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>14690</v>
+        <v>12880</v>
       </c>
       <c r="J10" t="n">
-        <v>4818.27</v>
+        <v>4797.53</v>
       </c>
     </row>
     <row r="11">
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1403.34</v>
+        <v>1394.83</v>
       </c>
       <c r="J11" t="n">
         <v>239.97</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>931.24</v>
+        <v>878.84</v>
       </c>
       <c r="J7" t="n">
         <v>187.56</v>
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1262000</v>
+        <v>1272000</v>
       </c>
       <c r="J8" t="n">
         <v>488486.58</v>
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>210000</v>
+        <v>215500</v>
       </c>
       <c r="J9" t="n">
         <v>74718.08</v>
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>12880</v>
+        <v>13375</v>
       </c>
       <c r="J10" t="n">
         <v>4797.53</v>
@@ -3944,10 +3944,10 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1394.83</v>
+        <v>1299.3</v>
       </c>
       <c r="J11" t="n">
-        <v>239.97</v>
+        <v>241.9</v>
       </c>
     </row>
   </sheetData>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>878.84</v>
+        <v>904.9</v>
       </c>
       <c r="J7" t="n">
         <v>187.56</v>
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1272000</v>
+        <v>1277000</v>
       </c>
       <c r="J8" t="n">
-        <v>488486.58</v>
+        <v>478040.22</v>
       </c>
     </row>
     <row r="9">
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>215500</v>
+        <v>218000</v>
       </c>
       <c r="J9" t="n">
         <v>74718.08</v>
@@ -3910,10 +3910,10 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>13375</v>
+        <v>13600</v>
       </c>
       <c r="J10" t="n">
-        <v>4797.53</v>
+        <v>4767.88</v>
       </c>
     </row>
     <row r="11">
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1299.3</v>
+        <v>1371.12</v>
       </c>
       <c r="J11" t="n">
         <v>241.9</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>904.9</v>
+        <v>913.67</v>
       </c>
       <c r="J7" t="n">
         <v>187.56</v>
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1277000</v>
+        <v>1294000</v>
       </c>
       <c r="J8" t="n">
-        <v>478040.22</v>
+        <v>492212.92</v>
       </c>
     </row>
     <row r="9">
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>218000</v>
+        <v>223500</v>
       </c>
       <c r="J9" t="n">
         <v>74718.08</v>
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>13600</v>
+        <v>13510</v>
       </c>
       <c r="J10" t="n">
         <v>4767.88</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1371.12</v>
+        <v>1378.22</v>
       </c>
       <c r="J11" t="n">
         <v>241.9</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,10 +3808,10 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>913.67</v>
+        <v>877.55</v>
       </c>
       <c r="J7" t="n">
-        <v>187.56</v>
+        <v>187.84</v>
       </c>
     </row>
     <row r="8">
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1294000</v>
+        <v>1277000</v>
       </c>
       <c r="J8" t="n">
         <v>492212.92</v>
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>223500</v>
+        <v>215500</v>
       </c>
       <c r="J9" t="n">
         <v>74718.08</v>
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>13510</v>
+        <v>12755</v>
       </c>
       <c r="J10" t="n">
         <v>4767.88</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1378.22</v>
+        <v>1238.03</v>
       </c>
       <c r="J11" t="n">
         <v>241.9</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>877.55</v>
+        <v>903.7</v>
       </c>
       <c r="J7" t="n">
         <v>187.84</v>
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1277000</v>
+        <v>1275000</v>
       </c>
       <c r="J8" t="n">
-        <v>492212.92</v>
+        <v>492212.9</v>
       </c>
     </row>
     <row r="9">
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>215500</v>
+        <v>213000</v>
       </c>
       <c r="J9" t="n">
         <v>74718.08</v>
@@ -3910,10 +3910,10 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>12755</v>
+        <v>12550</v>
       </c>
       <c r="J10" t="n">
-        <v>4767.88</v>
+        <v>4767.93</v>
       </c>
     </row>
     <row r="11">
@@ -3944,10 +3944,10 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1238.03</v>
+        <v>1255.58</v>
       </c>
       <c r="J11" t="n">
-        <v>241.9</v>
+        <v>242.67</v>
       </c>
     </row>
   </sheetData>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>903.7</v>
+        <v>928.76</v>
       </c>
       <c r="J7" t="n">
         <v>187.84</v>
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1275000</v>
+        <v>1341000</v>
       </c>
       <c r="J8" t="n">
-        <v>492212.9</v>
+        <v>492212.92</v>
       </c>
     </row>
     <row r="9">
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>213000</v>
+        <v>222000</v>
       </c>
       <c r="J9" t="n">
         <v>74718.08</v>
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>12550</v>
+        <v>12605</v>
       </c>
       <c r="J10" t="n">
         <v>4767.93</v>
@@ -3944,10 +3944,10 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1255.58</v>
+        <v>1304.84</v>
       </c>
       <c r="J11" t="n">
-        <v>242.67</v>
+        <v>242.8</v>
       </c>
     </row>
   </sheetData>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>928.76</v>
+        <v>983.23</v>
       </c>
       <c r="J7" t="n">
         <v>187.84</v>
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1341000</v>
+        <v>1487000</v>
       </c>
       <c r="J8" t="n">
-        <v>492212.92</v>
+        <v>522843.87</v>
       </c>
     </row>
     <row r="9">
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>222000</v>
+        <v>242000</v>
       </c>
       <c r="J9" t="n">
         <v>74718.08</v>
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>12605</v>
+        <v>14340</v>
       </c>
       <c r="J10" t="n">
         <v>4767.93</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1304.84</v>
+        <v>1404.77</v>
       </c>
       <c r="J11" t="n">
         <v>242.8</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>983.23</v>
+        <v>934.27</v>
       </c>
       <c r="J7" t="n">
         <v>187.84</v>
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1487000</v>
+        <v>1526000</v>
       </c>
       <c r="J8" t="n">
-        <v>522843.87</v>
+        <v>516001.05</v>
       </c>
     </row>
     <row r="9">
@@ -3876,10 +3876,10 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>242000</v>
+        <v>232000</v>
       </c>
       <c r="J9" t="n">
-        <v>74718.08</v>
+        <v>75588.39999999999</v>
       </c>
     </row>
     <row r="10">
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>14340</v>
+        <v>14505</v>
       </c>
       <c r="J10" t="n">
         <v>4767.93</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1404.77</v>
+        <v>1330.05</v>
       </c>
       <c r="J11" t="n">
         <v>242.8</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,10 +3808,10 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>934.27</v>
+        <v>884.74</v>
       </c>
       <c r="J7" t="n">
-        <v>187.84</v>
+        <v>187.93</v>
       </c>
     </row>
     <row r="8">
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1526000</v>
+        <v>1418000</v>
       </c>
       <c r="J8" t="n">
         <v>516001.05</v>
@@ -3876,10 +3876,10 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>232000</v>
+        <v>225000</v>
       </c>
       <c r="J9" t="n">
-        <v>75588.39999999999</v>
+        <v>76128.66</v>
       </c>
     </row>
     <row r="10">
@@ -3910,10 +3910,10 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>14505</v>
+        <v>13470</v>
       </c>
       <c r="J10" t="n">
-        <v>4767.93</v>
+        <v>5023.96</v>
       </c>
     </row>
     <row r="11">
@@ -3944,10 +3944,10 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1330.05</v>
+        <v>1150.89</v>
       </c>
       <c r="J11" t="n">
-        <v>242.8</v>
+        <v>257.87</v>
       </c>
     </row>
   </sheetData>
